--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -1,131 +1,468 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="4180" windowWidth="32770" windowHeight="16910"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>searchRange</t>
+  </si>
+  <si>
+    <t>skillArea</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>cd</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>skillType</t>
+  </si>
+  <si>
+    <t>flyObjectId</t>
+  </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>#备注行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>索敌范围</t>
+  </si>
+  <si>
+    <t>伤害范围</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>是否是普工</t>
+  </si>
+  <si>
+    <t>1近战2远程</t>
+  </si>
+  <si>
+    <t>飞行物ID</t>
   </si>
   <si>
     <t>刀盾近战</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>索敌范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冷却</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否是普工</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>skillArea</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓手远程</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -133,24 +470,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -408,102 +1031,119 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="18.08203125" customWidth="1"/>
-    <col min="3" max="3" width="19.4140625" customWidth="1"/>
-    <col min="5" max="5" width="32.83203125" customWidth="1"/>
-    <col min="6" max="6" width="29.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="19.4166666666667" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="32.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="24.625" customWidth="1"/>
+    <col min="8" max="8" width="31.375" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -515,14 +1155,49 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\unityProjects\GameWorldIsMine\WorldIsMine\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11780"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>id</t>
   </si>
@@ -38,6 +43,9 @@
     <t>searchRange</t>
   </si>
   <si>
+    <t>atkRange</t>
+  </si>
+  <si>
     <t>skillArea</t>
   </si>
   <si>
@@ -74,6 +82,9 @@
     <t>索敌范围</t>
   </si>
   <si>
+    <t>攻击范围</t>
+  </si>
+  <si>
     <t>伤害范围</t>
   </si>
   <si>
@@ -98,23 +109,20 @@
     <t>弓手远程</t>
   </si>
   <si>
-    <t>atkRange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>骑士攻击近战</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,21 +131,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -145,17 +477,306 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -417,24 +1038,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="18.08203125" customWidth="1"/>
-    <col min="3" max="4" width="19.4140625" customWidth="1"/>
-    <col min="5" max="5" width="20.58203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="29.83203125" customWidth="1"/>
-    <col min="8" max="8" width="24.58203125" customWidth="1"/>
-    <col min="9" max="9" width="31.33203125" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.0833333333333" customWidth="1"/>
+    <col min="3" max="4" width="19.4166666666667" customWidth="1"/>
+    <col min="5" max="5" width="20.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="32.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="29.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="24.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="31.3333333333333" customWidth="1"/>
+    <col min="10" max="10" width="12.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -448,89 +1069,89 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -538,13 +1159,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -570,13 +1191,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -597,8 +1218,40 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\unityProjects\GameWorldIsMine\WorldIsMine\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11780"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="SkillCfg" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -110,8 +115,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,21 +131,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -142,17 +477,306 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -414,24 +1038,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="18.08203125" customWidth="1"/>
-    <col min="3" max="4" width="19.4140625" customWidth="1"/>
-    <col min="5" max="5" width="20.58203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="29.83203125" customWidth="1"/>
-    <col min="8" max="8" width="24.58203125" customWidth="1"/>
-    <col min="9" max="9" width="31.33203125" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.0833333333333" customWidth="1"/>
+    <col min="3" max="4" width="19.4166666666667" customWidth="1"/>
+    <col min="5" max="5" width="20.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="32.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="29.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="24.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="31.3333333333333" customWidth="1"/>
+    <col min="10" max="10" width="12.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -627,7 +1251,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>id</t>
   </si>
@@ -108,6 +108,58 @@
   </si>
   <si>
     <t>英雄技能-冰霜冲击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法特效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吕布普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘备普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关羽普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>张飞普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赵云普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项羽普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刘邦普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩信普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>樊哙普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项庄普攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startEffect</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -424,21 +476,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="2" width="18.08203125" customWidth="1"/>
-    <col min="3" max="4" width="19.4140625" customWidth="1"/>
-    <col min="5" max="5" width="20.58203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="29.83203125" customWidth="1"/>
-    <col min="8" max="8" width="24.58203125" customWidth="1"/>
-    <col min="9" max="9" width="31.33203125" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="2" max="3" width="18.08203125" customWidth="1"/>
+    <col min="4" max="5" width="19.4140625" customWidth="1"/>
+    <col min="6" max="6" width="20.58203125" customWidth="1"/>
+    <col min="7" max="7" width="32.83203125" customWidth="1"/>
+    <col min="8" max="8" width="29.83203125" customWidth="1"/>
+    <col min="9" max="9" width="24.58203125" customWidth="1"/>
+    <col min="10" max="10" width="31.33203125" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,31 +498,34 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -478,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -487,13 +542,13 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>12</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
@@ -501,8 +556,11 @@
       <c r="J2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -510,156 +568,239 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>50</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="C5">
-        <v>150</v>
-      </c>
       <c r="D5">
         <v>150</v>
       </c>
       <c r="E5">
+        <v>150</v>
+      </c>
+      <c r="F5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>2</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
       <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>2</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>50</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
         <v>2</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
       <c r="I6">
         <v>1</v>
       </c>
       <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="C7">
-        <v>50</v>
-      </c>
       <c r="D7">
         <v>50</v>
       </c>
       <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
         <v>30</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
       <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>20</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
       </c>
       <c r="J7">
         <v>2</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
   <si>
     <t>id</t>
   </si>
@@ -107,10 +107,6 @@
     <t>骑士攻击近战</t>
   </si>
   <si>
-    <t>英雄技能-冰霜冲击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -160,6 +156,59 @@
   </si>
   <si>
     <t>startEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰风暴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电闪雷鸣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞龙在天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂风箭雨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狂龙吼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天下无双</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>des</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tring</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>燕人咆哮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -167,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,6 +227,14 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -202,8 +259,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -476,67 +534,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="2" max="3" width="18.08203125" customWidth="1"/>
-    <col min="4" max="5" width="19.4140625" customWidth="1"/>
-    <col min="6" max="6" width="20.58203125" customWidth="1"/>
-    <col min="7" max="7" width="32.83203125" customWidth="1"/>
-    <col min="8" max="8" width="29.83203125" customWidth="1"/>
-    <col min="9" max="9" width="24.58203125" customWidth="1"/>
-    <col min="10" max="10" width="31.33203125" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="2" max="4" width="18.08203125" customWidth="1"/>
+    <col min="5" max="6" width="19.4140625" customWidth="1"/>
+    <col min="7" max="7" width="20.58203125" customWidth="1"/>
+    <col min="8" max="8" width="32.83203125" customWidth="1"/>
+    <col min="9" max="9" width="29.83203125" customWidth="1"/>
+    <col min="10" max="10" width="24.58203125" customWidth="1"/>
+    <col min="11" max="11" width="31.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>39</v>
+      <c r="C1" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
       <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>27</v>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -545,13 +606,13 @@
         <v>12</v>
       </c>
       <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
@@ -559,252 +620,693 @@
       <c r="K2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>28</v>
+      <c r="C3" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="D4">
-        <v>50</v>
-      </c>
       <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4">
         <v>3</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="D5">
-        <v>150</v>
-      </c>
       <c r="E5">
         <v>150</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="D6">
-        <v>50</v>
-      </c>
       <c r="E6">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E7">
         <v>50</v>
       </c>
       <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7">
         <v>30</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>20</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>29</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>33</v>
+      </c>
+      <c r="E13">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>5</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15">
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>35</v>
+      </c>
+      <c r="E15">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16">
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>36</v>
+      </c>
+      <c r="E16">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17">
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="E17">
+        <v>50</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="E19">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20">
+        <v>50</v>
+      </c>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21">
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="E22">
+        <v>50</v>
+      </c>
+      <c r="F22">
+        <v>5</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>2</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E23">
+        <v>50</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excels/Skill.xlsx
+++ b/Excels/Skill.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
   <si>
     <t>id</t>
   </si>
@@ -209,6 +209,34 @@
   </si>
   <si>
     <t>燕人咆哮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风卷残云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buffId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>buff信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dieType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡方式（）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -534,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
@@ -546,9 +574,10 @@
     <col min="10" max="10" width="24.58203125" customWidth="1"/>
     <col min="11" max="11" width="31.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" customWidth="1"/>
+    <col min="14" max="14" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -585,8 +614,14 @@
       <c r="L1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -623,8 +658,14 @@
       <c r="L2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -661,8 +702,14 @@
       <c r="L3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>1</v>
       </c>
@@ -693,8 +740,11 @@
       <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>2</v>
       </c>
@@ -725,8 +775,11 @@
       <c r="L5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>3</v>
       </c>
@@ -757,8 +810,11 @@
       <c r="L6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>4</v>
       </c>
@@ -789,8 +845,11 @@
       <c r="L7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>5</v>
       </c>
@@ -821,8 +880,11 @@
       <c r="L8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>6</v>
       </c>
@@ -853,8 +915,11 @@
       <c r="L9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>7</v>
       </c>
@@ -885,8 +950,11 @@
       <c r="L10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>8</v>
       </c>
@@ -917,8 +985,11 @@
       <c r="L11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>9</v>
       </c>
@@ -949,8 +1020,11 @@
       <c r="L12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>10</v>
       </c>
@@ -981,8 +1055,11 @@
       <c r="L13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1013,8 +1090,11 @@
       <c r="L14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1045,8 +1125,11 @@
       <c r="L15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>13</v>
       </c>
@@ -1077,8 +1160,11 @@
       <c r="L16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1109,8 +1195,11 @@
       <c r="L17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1141,8 +1230,11 @@
       <c r="L18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1174,8 +1266,11 @@
       <c r="L19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1206,8 +1301,11 @@
       <c r="L20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1238,8 +1336,11 @@
       <c r="L21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1271,8 +1372,11 @@
       <c r="L22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="M22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1301,6 +1405,44 @@
         <v>1</v>
       </c>
       <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24">
+        <v>50</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>2</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>0</v>
       </c>
     </row>
